--- a/Cuentas(Recuperado automáticamente)(Recuperado automáticamente)(Recuperado automáticamente).xlsx
+++ b/Cuentas(Recuperado automáticamente)(Recuperado automáticamente)(Recuperado automáticamente).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83BEFE9-DA38-43AE-82B2-39645604076F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E7B4AD-3381-4F5A-BF4B-76949AAE1151}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" activeTab="1" xr2:uid="{C3415AEA-9BD2-4E48-A53C-D8D3F84FBBF2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{C3415AEA-9BD2-4E48-A53C-D8D3F84FBBF2}"/>
   </bookViews>
   <sheets>
     <sheet name="INGRESOS" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,12 @@
     <sheet name="CUENTAS CONTABLES" sheetId="6" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">INGRESOS!$A$3:$A$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">INGRESOS!$A$3:$A$345</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'REPORTE CAJA'!$A$80:$P$80</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId10"/>
+    <pivotCache cacheId="0" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4163" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4420" uniqueCount="802">
   <si>
     <t>DIARIO DE INGRESOS</t>
   </si>
@@ -2371,6 +2371,81 @@
   </si>
   <si>
     <t>LOURDES</t>
+  </si>
+  <si>
+    <t>COMIDA KAI</t>
+  </si>
+  <si>
+    <t>MOTOTRIZADO</t>
+  </si>
+  <si>
+    <t>AMADA</t>
+  </si>
+  <si>
+    <t>BERREZUETA</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>GUAMAN</t>
+  </si>
+  <si>
+    <t>ALLISON</t>
+  </si>
+  <si>
+    <t>JADAN</t>
+  </si>
+  <si>
+    <t>CANCELAdo</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>PLACENCIA</t>
+  </si>
+  <si>
+    <t>HYLO</t>
+  </si>
+  <si>
+    <t>CUERPO EXTRAÑO</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>CERTIFICADOS</t>
+  </si>
+  <si>
+    <t>COMIDA BRYAM</t>
+  </si>
+  <si>
+    <t>XAVI PINTADO KAI</t>
+  </si>
+  <si>
+    <t>LUNAS ALEPSA</t>
+  </si>
+  <si>
+    <t>PAGO IEES</t>
+  </si>
+  <si>
+    <t>BRYAM JEP</t>
+  </si>
+  <si>
+    <t>CRUCE CUENTAS KAI|</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>CRUCE MAQUINA</t>
+  </si>
+  <si>
+    <t>MAQUINA TARJETAS</t>
+  </si>
+  <si>
+    <t>CACNELADO</t>
   </si>
 </sst>
 </file>
@@ -5573,7 +5648,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Bryam" refreshedDate="45548.677037615744" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{28F5B5D8-F809-458F-82D2-A5FF6EE5F235}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A3:L316" sheet="INGRESOS"/>
+    <worksheetSource ref="A3:L345" sheet="INGRESOS"/>
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="FECHA" numFmtId="14">
@@ -5771,7 +5846,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB1F1147-B001-4D9B-823A-76427D932796}" name="TablaDinámica3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB1F1147-B001-4D9B-823A-76427D932796}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A10:A13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField numFmtId="14" showAll="0"/>
@@ -5824,8 +5899,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E6EA0A80-4895-441F-BC83-1C72F69279FD}" name="Tabla5" displayName="Tabla5" ref="A3:O316" totalsRowShown="0">
-  <autoFilter ref="A3:O316" xr:uid="{E6EA0A80-4895-441F-BC83-1C72F69279FD}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E6EA0A80-4895-441F-BC83-1C72F69279FD}" name="Tabla5" displayName="Tabla5" ref="A3:O345" totalsRowShown="0">
+  <autoFilter ref="A3:O345" xr:uid="{E6EA0A80-4895-441F-BC83-1C72F69279FD}">
     <filterColumn colId="0">
       <filters>
         <dateGroupItem year="2026" month="2" dateTimeGrouping="month"/>
@@ -5864,8 +5939,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{08600766-D8CB-4CE3-8841-691B0C200203}" name="Tabla8" displayName="Tabla8" ref="A3:L387" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
-  <autoFilter ref="A3:L387" xr:uid="{08600766-D8CB-4CE3-8841-691B0C200203}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{08600766-D8CB-4CE3-8841-691B0C200203}" name="Tabla8" displayName="Tabla8" ref="A3:L426" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
+  <autoFilter ref="A3:L426" xr:uid="{08600766-D8CB-4CE3-8841-691B0C200203}"/>
   <sortState ref="A4:L379">
     <sortCondition ref="A4:A379"/>
   </sortState>
@@ -6278,7 +6353,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O316"/>
+  <dimension ref="A1:O345"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.5703125" customWidth="1"/>
@@ -16880,7 +16955,7 @@
     </row>
     <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280" s="77">
-        <v>46149</v>
+        <v>46146</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>168</v>
@@ -18278,12 +18353,32 @@
     </row>
     <row r="316" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A316" s="77">
-        <v>46177</v>
-      </c>
-      <c r="B316" s="3"/>
+        <v>46179</v>
+      </c>
+      <c r="B316" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="C316" t="s">
+        <v>780</v>
+      </c>
+      <c r="D316" t="s">
+        <v>17</v>
+      </c>
+      <c r="E316">
+        <v>1</v>
+      </c>
+      <c r="F316">
+        <v>90</v>
+      </c>
       <c r="G316" s="78">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H316" t="s">
+        <v>37</v>
+      </c>
+      <c r="J316" t="s">
+        <v>18</v>
       </c>
       <c r="K316" s="78" t="str">
         <f t="shared" si="42"/>
@@ -18294,6 +18389,950 @@
         <v>2026</v>
       </c>
       <c r="O316" s="79"/>
+    </row>
+    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A317" s="77">
+        <v>46179</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C317" t="s">
+        <v>70</v>
+      </c>
+      <c r="D317" t="s">
+        <v>70</v>
+      </c>
+      <c r="E317">
+        <v>1</v>
+      </c>
+      <c r="F317">
+        <v>5</v>
+      </c>
+      <c r="G317" s="78">
+        <f t="shared" ref="G317:G321" si="44">E317*F317</f>
+        <v>5</v>
+      </c>
+      <c r="H317" t="s">
+        <v>606</v>
+      </c>
+      <c r="J317" t="s">
+        <v>18</v>
+      </c>
+      <c r="K317" s="78" t="str">
+        <f>UPPER(TEXT(A317,"MMMM"))</f>
+        <v>JUNIO</v>
+      </c>
+      <c r="L317" s="78">
+        <f t="shared" ref="L317:L321" si="45">+YEAR(A317)</f>
+        <v>2026</v>
+      </c>
+      <c r="O317" s="79"/>
+    </row>
+    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A318" s="77">
+        <v>46179</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C318" t="s">
+        <v>781</v>
+      </c>
+      <c r="D318" t="s">
+        <v>17</v>
+      </c>
+      <c r="E318">
+        <v>1</v>
+      </c>
+      <c r="F318">
+        <v>20</v>
+      </c>
+      <c r="G318" s="78">
+        <f t="shared" si="44"/>
+        <v>20</v>
+      </c>
+      <c r="H318" t="s">
+        <v>37</v>
+      </c>
+      <c r="J318" t="s">
+        <v>18</v>
+      </c>
+      <c r="K318" s="78" t="str">
+        <f t="shared" ref="K318:K321" si="46">UPPER(TEXT(A318,"MMMM"))</f>
+        <v>JUNIO</v>
+      </c>
+      <c r="L318" s="78">
+        <f t="shared" si="45"/>
+        <v>2026</v>
+      </c>
+      <c r="O318" s="79"/>
+    </row>
+    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A319" s="77">
+        <v>46181</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C319" t="s">
+        <v>782</v>
+      </c>
+      <c r="D319" t="s">
+        <v>17</v>
+      </c>
+      <c r="E319">
+        <v>1</v>
+      </c>
+      <c r="F319">
+        <v>130</v>
+      </c>
+      <c r="G319" s="78">
+        <f t="shared" si="44"/>
+        <v>130</v>
+      </c>
+      <c r="H319" t="s">
+        <v>37</v>
+      </c>
+      <c r="J319" t="s">
+        <v>18</v>
+      </c>
+      <c r="K319" s="78" t="str">
+        <f t="shared" si="46"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L319" s="78">
+        <f t="shared" si="45"/>
+        <v>2026</v>
+      </c>
+      <c r="O319" s="79"/>
+    </row>
+    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A320" s="77">
+        <v>46181</v>
+      </c>
+      <c r="B320" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="C320" t="s">
+        <v>784</v>
+      </c>
+      <c r="D320" t="s">
+        <v>17</v>
+      </c>
+      <c r="E320">
+        <v>1</v>
+      </c>
+      <c r="F320">
+        <v>235</v>
+      </c>
+      <c r="G320" s="78">
+        <f t="shared" si="44"/>
+        <v>235</v>
+      </c>
+      <c r="H320" t="s">
+        <v>606</v>
+      </c>
+      <c r="J320" t="s">
+        <v>18</v>
+      </c>
+      <c r="K320" s="78" t="str">
+        <f t="shared" si="46"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L320" s="78">
+        <f t="shared" si="45"/>
+        <v>2026</v>
+      </c>
+      <c r="O320" s="79"/>
+    </row>
+    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A321" s="77">
+        <v>46181</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="C321" t="s">
+        <v>258</v>
+      </c>
+      <c r="D321" t="s">
+        <v>17</v>
+      </c>
+      <c r="E321">
+        <v>1</v>
+      </c>
+      <c r="F321">
+        <v>110</v>
+      </c>
+      <c r="G321" s="78">
+        <f t="shared" si="44"/>
+        <v>110</v>
+      </c>
+      <c r="H321" t="s">
+        <v>606</v>
+      </c>
+      <c r="J321" t="s">
+        <v>18</v>
+      </c>
+      <c r="K321" s="78" t="str">
+        <f t="shared" si="46"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L321" s="78">
+        <f t="shared" si="45"/>
+        <v>2026</v>
+      </c>
+      <c r="O321" s="79"/>
+    </row>
+    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A322" s="77">
+        <v>46182</v>
+      </c>
+      <c r="B322" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C322" t="s">
+        <v>543</v>
+      </c>
+      <c r="D322" t="s">
+        <v>17</v>
+      </c>
+      <c r="E322">
+        <v>1</v>
+      </c>
+      <c r="F322">
+        <v>10</v>
+      </c>
+      <c r="G322" s="78">
+        <f t="shared" ref="G322:G328" si="47">E322*F322</f>
+        <v>10</v>
+      </c>
+      <c r="H322" t="s">
+        <v>785</v>
+      </c>
+      <c r="J322" t="s">
+        <v>18</v>
+      </c>
+      <c r="K322" s="78" t="str">
+        <f t="shared" ref="K322:K328" si="48">UPPER(TEXT(A322,"MMMM"))</f>
+        <v>JUNIO</v>
+      </c>
+      <c r="L322" s="78">
+        <f t="shared" ref="L322:L328" si="49">+YEAR(A322)</f>
+        <v>2026</v>
+      </c>
+      <c r="O322" s="79"/>
+    </row>
+    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A323" s="77">
+        <v>46183</v>
+      </c>
+      <c r="B323" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C323" t="s">
+        <v>493</v>
+      </c>
+      <c r="D323" t="s">
+        <v>17</v>
+      </c>
+      <c r="E323">
+        <v>1</v>
+      </c>
+      <c r="F323">
+        <v>100</v>
+      </c>
+      <c r="G323" s="78">
+        <f t="shared" si="47"/>
+        <v>100</v>
+      </c>
+      <c r="H323" t="s">
+        <v>606</v>
+      </c>
+      <c r="J323" t="s">
+        <v>18</v>
+      </c>
+      <c r="K323" s="78" t="str">
+        <f t="shared" si="48"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L323" s="78">
+        <f t="shared" si="49"/>
+        <v>2026</v>
+      </c>
+      <c r="O323" s="79"/>
+    </row>
+    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A324" s="77">
+        <v>46183</v>
+      </c>
+      <c r="B324" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="C324" t="s">
+        <v>787</v>
+      </c>
+      <c r="D324" t="s">
+        <v>17</v>
+      </c>
+      <c r="E324">
+        <v>1</v>
+      </c>
+      <c r="F324">
+        <v>95</v>
+      </c>
+      <c r="G324" s="78">
+        <f t="shared" si="47"/>
+        <v>95</v>
+      </c>
+      <c r="H324" t="s">
+        <v>606</v>
+      </c>
+      <c r="J324" t="s">
+        <v>18</v>
+      </c>
+      <c r="K324" s="78" t="str">
+        <f t="shared" si="48"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L324" s="78">
+        <f t="shared" si="49"/>
+        <v>2026</v>
+      </c>
+      <c r="O324" s="79"/>
+    </row>
+    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A325" s="77">
+        <v>46183</v>
+      </c>
+      <c r="B325" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="D325" t="s">
+        <v>70</v>
+      </c>
+      <c r="E325">
+        <v>1</v>
+      </c>
+      <c r="F325">
+        <v>20</v>
+      </c>
+      <c r="G325" s="78">
+        <f t="shared" si="47"/>
+        <v>20</v>
+      </c>
+      <c r="H325" t="s">
+        <v>606</v>
+      </c>
+      <c r="J325" t="s">
+        <v>18</v>
+      </c>
+      <c r="K325" s="78" t="str">
+        <f t="shared" si="48"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L325" s="78">
+        <f t="shared" si="49"/>
+        <v>2026</v>
+      </c>
+      <c r="O325" s="79"/>
+    </row>
+    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A326" s="77">
+        <v>46184</v>
+      </c>
+      <c r="B326" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="D326" t="s">
+        <v>70</v>
+      </c>
+      <c r="E326">
+        <v>1</v>
+      </c>
+      <c r="F326">
+        <v>10</v>
+      </c>
+      <c r="G326" s="78">
+        <f t="shared" si="47"/>
+        <v>10</v>
+      </c>
+      <c r="H326" t="s">
+        <v>606</v>
+      </c>
+      <c r="J326" t="s">
+        <v>18</v>
+      </c>
+      <c r="K326" s="78" t="str">
+        <f t="shared" si="48"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L326" s="78">
+        <f t="shared" si="49"/>
+        <v>2026</v>
+      </c>
+      <c r="O326" s="79"/>
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A327" s="77">
+        <v>46184</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="C327" t="s">
+        <v>696</v>
+      </c>
+      <c r="D327" t="s">
+        <v>17</v>
+      </c>
+      <c r="E327">
+        <v>1</v>
+      </c>
+      <c r="F327">
+        <v>40</v>
+      </c>
+      <c r="G327" s="78">
+        <f t="shared" si="47"/>
+        <v>40</v>
+      </c>
+      <c r="H327" t="s">
+        <v>606</v>
+      </c>
+      <c r="J327" t="s">
+        <v>18</v>
+      </c>
+      <c r="K327" s="78" t="str">
+        <f t="shared" si="48"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L327" s="78">
+        <f t="shared" si="49"/>
+        <v>2026</v>
+      </c>
+      <c r="O327" s="79"/>
+    </row>
+    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A328" s="77">
+        <v>46184</v>
+      </c>
+      <c r="B328" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="D328" t="s">
+        <v>21</v>
+      </c>
+      <c r="E328">
+        <v>2</v>
+      </c>
+      <c r="F328">
+        <v>5</v>
+      </c>
+      <c r="G328" s="78">
+        <f t="shared" si="47"/>
+        <v>10</v>
+      </c>
+      <c r="H328" t="s">
+        <v>606</v>
+      </c>
+      <c r="J328" t="s">
+        <v>18</v>
+      </c>
+      <c r="K328" s="78" t="str">
+        <f t="shared" si="48"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L328" s="78">
+        <f t="shared" si="49"/>
+        <v>2026</v>
+      </c>
+      <c r="O328" s="79"/>
+    </row>
+    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A329" s="77">
+        <v>46177</v>
+      </c>
+      <c r="B329" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D329" t="s">
+        <v>17</v>
+      </c>
+      <c r="E329">
+        <v>1</v>
+      </c>
+      <c r="F329">
+        <v>60</v>
+      </c>
+      <c r="G329" s="78">
+        <f t="shared" ref="G329:G332" si="50">E329*F329</f>
+        <v>60</v>
+      </c>
+      <c r="H329" t="s">
+        <v>606</v>
+      </c>
+      <c r="J329" t="s">
+        <v>27</v>
+      </c>
+      <c r="K329" s="78" t="str">
+        <f t="shared" ref="K329:K332" si="51">UPPER(TEXT(A329,"MMMM"))</f>
+        <v>JUNIO</v>
+      </c>
+      <c r="L329" s="78">
+        <f t="shared" ref="L329:L332" si="52">+YEAR(A329)</f>
+        <v>2026</v>
+      </c>
+      <c r="O329" s="79"/>
+    </row>
+    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A330" s="77">
+        <v>46181</v>
+      </c>
+      <c r="B330" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D330" t="s">
+        <v>17</v>
+      </c>
+      <c r="E330">
+        <v>1</v>
+      </c>
+      <c r="F330">
+        <v>80</v>
+      </c>
+      <c r="G330" s="78">
+        <f t="shared" si="50"/>
+        <v>80</v>
+      </c>
+      <c r="H330" t="s">
+        <v>606</v>
+      </c>
+      <c r="J330" t="s">
+        <v>27</v>
+      </c>
+      <c r="K330" s="78" t="str">
+        <f t="shared" si="51"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L330" s="78">
+        <f t="shared" si="52"/>
+        <v>2026</v>
+      </c>
+      <c r="O330" s="79"/>
+    </row>
+    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A331" s="77">
+        <v>46182</v>
+      </c>
+      <c r="B331" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D331" t="s">
+        <v>17</v>
+      </c>
+      <c r="E331">
+        <v>1</v>
+      </c>
+      <c r="F331">
+        <v>1000</v>
+      </c>
+      <c r="G331" s="78">
+        <f t="shared" si="50"/>
+        <v>1000</v>
+      </c>
+      <c r="H331" t="s">
+        <v>606</v>
+      </c>
+      <c r="J331" t="s">
+        <v>27</v>
+      </c>
+      <c r="K331" s="78" t="str">
+        <f t="shared" si="51"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L331" s="78">
+        <f t="shared" si="52"/>
+        <v>2026</v>
+      </c>
+      <c r="O331" s="79"/>
+    </row>
+    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A332" s="77">
+        <v>46147</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="C332" t="s">
+        <v>740</v>
+      </c>
+      <c r="D332" t="s">
+        <v>17</v>
+      </c>
+      <c r="E332">
+        <v>1</v>
+      </c>
+      <c r="F332">
+        <v>115</v>
+      </c>
+      <c r="G332" s="78">
+        <f t="shared" si="50"/>
+        <v>115</v>
+      </c>
+      <c r="H332" t="s">
+        <v>606</v>
+      </c>
+      <c r="J332" t="s">
+        <v>83</v>
+      </c>
+      <c r="K332" s="78" t="str">
+        <f t="shared" si="51"/>
+        <v>MAYO</v>
+      </c>
+      <c r="L332" s="78">
+        <f t="shared" si="52"/>
+        <v>2026</v>
+      </c>
+      <c r="O332" s="79"/>
+    </row>
+    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A333" s="77">
+        <v>46173</v>
+      </c>
+      <c r="B333" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="D333" t="s">
+        <v>17</v>
+      </c>
+      <c r="E333">
+        <v>1</v>
+      </c>
+      <c r="F333">
+        <v>0.24</v>
+      </c>
+      <c r="G333" s="78">
+        <f t="shared" ref="G333:G337" si="53">E333*F333</f>
+        <v>0.24</v>
+      </c>
+      <c r="H333" t="s">
+        <v>606</v>
+      </c>
+      <c r="J333" t="s">
+        <v>83</v>
+      </c>
+      <c r="K333" s="78" t="str">
+        <f t="shared" ref="K333:K337" si="54">UPPER(TEXT(A333,"MMMM"))</f>
+        <v>MAYO</v>
+      </c>
+      <c r="L333" s="78">
+        <f t="shared" ref="L333:L337" si="55">+YEAR(A333)</f>
+        <v>2026</v>
+      </c>
+      <c r="O333" s="79"/>
+    </row>
+    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A334" s="77">
+        <v>46164</v>
+      </c>
+      <c r="B334" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D334" t="s">
+        <v>17</v>
+      </c>
+      <c r="E334">
+        <v>1</v>
+      </c>
+      <c r="F334">
+        <v>5</v>
+      </c>
+      <c r="G334" s="78">
+        <f t="shared" si="53"/>
+        <v>5</v>
+      </c>
+      <c r="H334" t="s">
+        <v>606</v>
+      </c>
+      <c r="J334" t="s">
+        <v>30</v>
+      </c>
+      <c r="K334" s="78" t="str">
+        <f t="shared" si="54"/>
+        <v>MAYO</v>
+      </c>
+      <c r="L334" s="78">
+        <f t="shared" si="55"/>
+        <v>2026</v>
+      </c>
+      <c r="O334" s="79"/>
+    </row>
+    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A335" s="77">
+        <v>46181</v>
+      </c>
+      <c r="B335" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="D335" t="s">
+        <v>17</v>
+      </c>
+      <c r="E335">
+        <v>1</v>
+      </c>
+      <c r="F335">
+        <v>250</v>
+      </c>
+      <c r="G335" s="78">
+        <f t="shared" si="53"/>
+        <v>250</v>
+      </c>
+      <c r="H335" t="s">
+        <v>606</v>
+      </c>
+      <c r="I335" t="s">
+        <v>799</v>
+      </c>
+      <c r="J335" t="s">
+        <v>30</v>
+      </c>
+      <c r="K335" s="78" t="str">
+        <f t="shared" si="54"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L335" s="78">
+        <f t="shared" si="55"/>
+        <v>2026</v>
+      </c>
+      <c r="O335" s="79"/>
+    </row>
+    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A336" s="77">
+        <v>46181</v>
+      </c>
+      <c r="B336" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D336" t="s">
+        <v>17</v>
+      </c>
+      <c r="E336">
+        <v>1</v>
+      </c>
+      <c r="F336">
+        <v>40</v>
+      </c>
+      <c r="G336" s="78">
+        <f t="shared" si="53"/>
+        <v>40</v>
+      </c>
+      <c r="H336" t="s">
+        <v>606</v>
+      </c>
+      <c r="J336" t="s">
+        <v>30</v>
+      </c>
+      <c r="K336" s="78" t="str">
+        <f t="shared" si="54"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L336" s="78">
+        <f t="shared" si="55"/>
+        <v>2026</v>
+      </c>
+      <c r="O336" s="79"/>
+    </row>
+    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A337" s="77">
+        <v>46182</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="D337" t="s">
+        <v>17</v>
+      </c>
+      <c r="E337">
+        <v>1</v>
+      </c>
+      <c r="F337">
+        <v>1000</v>
+      </c>
+      <c r="G337" s="78">
+        <f t="shared" si="53"/>
+        <v>1000</v>
+      </c>
+      <c r="H337" t="s">
+        <v>801</v>
+      </c>
+      <c r="I337" t="s">
+        <v>799</v>
+      </c>
+      <c r="J337" t="s">
+        <v>30</v>
+      </c>
+      <c r="K337" s="78" t="str">
+        <f t="shared" si="54"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L337" s="78">
+        <f t="shared" si="55"/>
+        <v>2026</v>
+      </c>
+      <c r="O337" s="79"/>
+    </row>
+    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A338" s="77">
+        <v>46182</v>
+      </c>
+      <c r="B338" s="3"/>
+      <c r="G338" s="78">
+        <f t="shared" ref="G338:G345" si="56">E338*F338</f>
+        <v>0</v>
+      </c>
+      <c r="K338" s="78" t="str">
+        <f t="shared" ref="K338:K345" si="57">UPPER(TEXT(A338,"MMMM"))</f>
+        <v>JUNIO</v>
+      </c>
+      <c r="L338" s="78">
+        <f t="shared" ref="L338:L345" si="58">+YEAR(A338)</f>
+        <v>2026</v>
+      </c>
+      <c r="O338" s="79"/>
+    </row>
+    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A339" s="77">
+        <v>46182</v>
+      </c>
+      <c r="B339" s="3"/>
+      <c r="G339" s="78">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="K339" s="78" t="str">
+        <f t="shared" si="57"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L339" s="78">
+        <f t="shared" si="58"/>
+        <v>2026</v>
+      </c>
+      <c r="O339" s="79"/>
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A340" s="77">
+        <v>46182</v>
+      </c>
+      <c r="B340" s="3"/>
+      <c r="G340" s="78">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="K340" s="78" t="str">
+        <f t="shared" si="57"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L340" s="78">
+        <f t="shared" si="58"/>
+        <v>2026</v>
+      </c>
+      <c r="O340" s="79"/>
+    </row>
+    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A341" s="77">
+        <v>46182</v>
+      </c>
+      <c r="B341" s="3"/>
+      <c r="G341" s="78">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="K341" s="78" t="str">
+        <f t="shared" si="57"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L341" s="78">
+        <f t="shared" si="58"/>
+        <v>2026</v>
+      </c>
+      <c r="O341" s="79"/>
+    </row>
+    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A342" s="77">
+        <v>46182</v>
+      </c>
+      <c r="B342" s="3"/>
+      <c r="G342" s="78">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="K342" s="78" t="str">
+        <f t="shared" si="57"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L342" s="78">
+        <f t="shared" si="58"/>
+        <v>2026</v>
+      </c>
+      <c r="O342" s="79"/>
+    </row>
+    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A343" s="77">
+        <v>46182</v>
+      </c>
+      <c r="B343" s="3"/>
+      <c r="G343" s="78">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="K343" s="78" t="str">
+        <f t="shared" si="57"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L343" s="78">
+        <f t="shared" si="58"/>
+        <v>2026</v>
+      </c>
+      <c r="O343" s="79"/>
+    </row>
+    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A344" s="77">
+        <v>46182</v>
+      </c>
+      <c r="B344" s="3"/>
+      <c r="G344" s="78">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="K344" s="78" t="str">
+        <f t="shared" si="57"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L344" s="78">
+        <f t="shared" si="58"/>
+        <v>2026</v>
+      </c>
+      <c r="O344" s="79"/>
+    </row>
+    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A345" s="77">
+        <v>46182</v>
+      </c>
+      <c r="B345" s="3"/>
+      <c r="G345" s="78">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="K345" s="78" t="str">
+        <f t="shared" si="57"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="L345" s="78">
+        <f t="shared" si="58"/>
+        <v>2026</v>
+      </c>
+      <c r="O345" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -18331,7 +19370,7 @@
           <x14:formula1>
             <xm:f>'CUENTAS CONTABLES'!$E$5:$E$10</xm:f>
           </x14:formula1>
-          <xm:sqref>D4:D316</xm:sqref>
+          <xm:sqref>D4:D345</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -18341,7 +19380,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81E9F279-1602-47A3-9742-752D431C92E6}">
-  <dimension ref="A1:M387"/>
+  <dimension ref="A1:M426"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -32605,17 +33644,27 @@
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A387" s="12">
-        <v>46179</v>
-      </c>
-      <c r="B387" s="68"/>
-      <c r="C387" s="13"/>
-      <c r="D387" s="14"/>
-      <c r="E387" s="15"/>
+        <v>46178</v>
+      </c>
+      <c r="B387" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="C387" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D387" s="14">
+        <v>1</v>
+      </c>
+      <c r="E387" s="15">
+        <v>50</v>
+      </c>
       <c r="F387" s="15">
         <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
-        <v>0</v>
-      </c>
-      <c r="G387" s="13"/>
+        <v>50</v>
+      </c>
+      <c r="G387" s="13" t="s">
+        <v>777</v>
+      </c>
       <c r="H387" s="13"/>
       <c r="I387" s="13" t="str">
         <f t="shared" si="22"/>
@@ -32625,8 +33674,1441 @@
         <f t="shared" si="23"/>
         <v>2026</v>
       </c>
-      <c r="K387" s="13"/>
+      <c r="K387" s="13" t="s">
+        <v>18</v>
+      </c>
       <c r="L387" s="13"/>
+    </row>
+    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A388" s="12">
+        <v>46178</v>
+      </c>
+      <c r="B388" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="C388" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D388" s="14">
+        <v>1</v>
+      </c>
+      <c r="E388" s="15">
+        <v>3.5</v>
+      </c>
+      <c r="F388" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>3.5</v>
+      </c>
+      <c r="G388" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H388" s="13"/>
+      <c r="I388" s="13" t="str">
+        <f t="shared" ref="I388:I394" si="24">UPPER(TEXT(A388,"MMMM"))</f>
+        <v>JUNIO</v>
+      </c>
+      <c r="J388" s="13">
+        <f t="shared" ref="J388:J394" si="25">+YEAR(A388)</f>
+        <v>2026</v>
+      </c>
+      <c r="K388" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L388" s="13"/>
+    </row>
+    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A389" s="12">
+        <v>46179</v>
+      </c>
+      <c r="B389" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="C389" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D389" s="14">
+        <v>1</v>
+      </c>
+      <c r="E389" s="15">
+        <v>30</v>
+      </c>
+      <c r="F389" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>30</v>
+      </c>
+      <c r="G389" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H389" s="13"/>
+      <c r="I389" s="13" t="str">
+        <f t="shared" si="24"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J389" s="13">
+        <f t="shared" si="25"/>
+        <v>2026</v>
+      </c>
+      <c r="K389" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L389" s="13"/>
+    </row>
+    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A390" s="12">
+        <v>46179</v>
+      </c>
+      <c r="B390" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C390" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D390" s="14">
+        <v>1</v>
+      </c>
+      <c r="E390" s="15">
+        <v>5</v>
+      </c>
+      <c r="F390" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>5</v>
+      </c>
+      <c r="G390" s="13" t="s">
+        <v>778</v>
+      </c>
+      <c r="H390" s="13"/>
+      <c r="I390" s="13" t="str">
+        <f t="shared" si="24"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J390" s="13">
+        <f t="shared" si="25"/>
+        <v>2026</v>
+      </c>
+      <c r="K390" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L390" s="13"/>
+    </row>
+    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A391" s="12">
+        <v>46181</v>
+      </c>
+      <c r="B391" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C391" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D391" s="14">
+        <v>1</v>
+      </c>
+      <c r="E391" s="15">
+        <v>6</v>
+      </c>
+      <c r="F391" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>6</v>
+      </c>
+      <c r="G391" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H391" s="13"/>
+      <c r="I391" s="13" t="str">
+        <f t="shared" si="24"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J391" s="13">
+        <f t="shared" si="25"/>
+        <v>2026</v>
+      </c>
+      <c r="K391" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L391" s="13"/>
+    </row>
+    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A392" s="12">
+        <v>46181</v>
+      </c>
+      <c r="B392" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="C392" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D392" s="14">
+        <v>1</v>
+      </c>
+      <c r="E392" s="15">
+        <v>6.5</v>
+      </c>
+      <c r="F392" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>6.5</v>
+      </c>
+      <c r="G392" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H392" s="13"/>
+      <c r="I392" s="13" t="str">
+        <f t="shared" si="24"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J392" s="13">
+        <f t="shared" si="25"/>
+        <v>2026</v>
+      </c>
+      <c r="K392" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L392" s="13"/>
+    </row>
+    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A393" s="12">
+        <v>46181</v>
+      </c>
+      <c r="B393" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C393" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D393" s="14">
+        <v>1</v>
+      </c>
+      <c r="E393" s="15">
+        <v>80</v>
+      </c>
+      <c r="F393" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>80</v>
+      </c>
+      <c r="G393" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="H393" s="13"/>
+      <c r="I393" s="13" t="str">
+        <f t="shared" si="24"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J393" s="13">
+        <f t="shared" si="25"/>
+        <v>2026</v>
+      </c>
+      <c r="K393" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L393" s="13"/>
+    </row>
+    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A394" s="12">
+        <v>46182</v>
+      </c>
+      <c r="B394" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="C394" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D394" s="14">
+        <v>1</v>
+      </c>
+      <c r="E394" s="15">
+        <v>3.8</v>
+      </c>
+      <c r="F394" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>3.8</v>
+      </c>
+      <c r="G394" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H394" s="13"/>
+      <c r="I394" s="13" t="str">
+        <f t="shared" si="24"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J394" s="13">
+        <f t="shared" si="25"/>
+        <v>2026</v>
+      </c>
+      <c r="K394" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L394" s="13"/>
+    </row>
+    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A395" s="12">
+        <v>46182</v>
+      </c>
+      <c r="B395" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C395" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D395" s="14">
+        <v>1</v>
+      </c>
+      <c r="E395" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="F395" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>2.5</v>
+      </c>
+      <c r="G395" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H395" s="13"/>
+      <c r="I395" s="13" t="str">
+        <f t="shared" ref="I395:I399" si="26">UPPER(TEXT(A395,"MMMM"))</f>
+        <v>JUNIO</v>
+      </c>
+      <c r="J395" s="13">
+        <f t="shared" ref="J395:J399" si="27">+YEAR(A395)</f>
+        <v>2026</v>
+      </c>
+      <c r="K395" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L395" s="13"/>
+    </row>
+    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A396" s="12">
+        <v>46182</v>
+      </c>
+      <c r="B396" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="C396" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D396" s="14">
+        <v>1</v>
+      </c>
+      <c r="E396" s="15">
+        <v>6</v>
+      </c>
+      <c r="F396" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>6</v>
+      </c>
+      <c r="G396" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="H396" s="13"/>
+      <c r="I396" s="13" t="str">
+        <f t="shared" si="26"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J396" s="13">
+        <f t="shared" si="27"/>
+        <v>2026</v>
+      </c>
+      <c r="K396" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L396" s="13"/>
+    </row>
+    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A397" s="12">
+        <v>46182</v>
+      </c>
+      <c r="B397" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C397" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D397" s="14">
+        <v>1</v>
+      </c>
+      <c r="E397" s="15">
+        <v>6.3</v>
+      </c>
+      <c r="F397" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>6.3</v>
+      </c>
+      <c r="G397" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H397" s="13"/>
+      <c r="I397" s="13" t="str">
+        <f t="shared" si="26"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J397" s="13">
+        <f t="shared" si="27"/>
+        <v>2026</v>
+      </c>
+      <c r="K397" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L397" s="13"/>
+    </row>
+    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A398" s="12">
+        <v>46183</v>
+      </c>
+      <c r="B398" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C398" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D398" s="14">
+        <v>1</v>
+      </c>
+      <c r="E398" s="15">
+        <v>11.3</v>
+      </c>
+      <c r="F398" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>11.3</v>
+      </c>
+      <c r="G398" s="13" t="s">
+        <v>670</v>
+      </c>
+      <c r="H398" s="13"/>
+      <c r="I398" s="13" t="str">
+        <f t="shared" si="26"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J398" s="13">
+        <f t="shared" si="27"/>
+        <v>2026</v>
+      </c>
+      <c r="K398" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L398" s="13"/>
+    </row>
+    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A399" s="12">
+        <v>46183</v>
+      </c>
+      <c r="B399" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C399" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D399" s="14">
+        <v>1</v>
+      </c>
+      <c r="E399" s="15">
+        <v>2</v>
+      </c>
+      <c r="F399" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>2</v>
+      </c>
+      <c r="G399" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H399" s="13"/>
+      <c r="I399" s="13" t="str">
+        <f t="shared" si="26"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J399" s="13">
+        <f t="shared" si="27"/>
+        <v>2026</v>
+      </c>
+      <c r="K399" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L399" s="13"/>
+    </row>
+    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A400" s="12">
+        <v>46183</v>
+      </c>
+      <c r="B400" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="C400" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D400" s="14">
+        <v>1</v>
+      </c>
+      <c r="E400" s="15">
+        <v>20</v>
+      </c>
+      <c r="F400" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>20</v>
+      </c>
+      <c r="G400" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H400" s="13"/>
+      <c r="I400" s="13" t="str">
+        <f t="shared" ref="I400:I402" si="28">UPPER(TEXT(A400,"MMMM"))</f>
+        <v>JUNIO</v>
+      </c>
+      <c r="J400" s="13">
+        <f t="shared" ref="J400:J402" si="29">+YEAR(A400)</f>
+        <v>2026</v>
+      </c>
+      <c r="K400" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L400" s="13"/>
+    </row>
+    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A401" s="12">
+        <v>46184</v>
+      </c>
+      <c r="B401" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C401" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D401" s="14">
+        <v>1</v>
+      </c>
+      <c r="E401" s="15">
+        <v>18</v>
+      </c>
+      <c r="F401" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>18</v>
+      </c>
+      <c r="G401" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="H401" s="13"/>
+      <c r="I401" s="13" t="str">
+        <f t="shared" si="28"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J401" s="13">
+        <f t="shared" si="29"/>
+        <v>2026</v>
+      </c>
+      <c r="K401" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L401" s="13"/>
+    </row>
+    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A402" s="12">
+        <v>46184</v>
+      </c>
+      <c r="B402" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="C402" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D402" s="14">
+        <v>1</v>
+      </c>
+      <c r="E402" s="15">
+        <v>2.75</v>
+      </c>
+      <c r="F402" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>2.75</v>
+      </c>
+      <c r="G402" s="13" t="s">
+        <v>751</v>
+      </c>
+      <c r="H402" s="13"/>
+      <c r="I402" s="13" t="str">
+        <f t="shared" si="28"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J402" s="13">
+        <f t="shared" si="29"/>
+        <v>2026</v>
+      </c>
+      <c r="K402" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L402" s="13"/>
+    </row>
+    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A403" s="12">
+        <v>46184</v>
+      </c>
+      <c r="B403" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="C403" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D403" s="14">
+        <v>1</v>
+      </c>
+      <c r="E403" s="15">
+        <v>20</v>
+      </c>
+      <c r="F403" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>20</v>
+      </c>
+      <c r="G403" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="H403" s="13"/>
+      <c r="I403" s="13" t="str">
+        <f t="shared" ref="I403:I406" si="30">UPPER(TEXT(A403,"MMMM"))</f>
+        <v>JUNIO</v>
+      </c>
+      <c r="J403" s="13">
+        <f t="shared" ref="J403:J406" si="31">+YEAR(A403)</f>
+        <v>2026</v>
+      </c>
+      <c r="K403" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L403" s="13"/>
+    </row>
+    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A404" s="12">
+        <v>46185</v>
+      </c>
+      <c r="B404" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="C404" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D404" s="14">
+        <v>1</v>
+      </c>
+      <c r="E404" s="15">
+        <v>550</v>
+      </c>
+      <c r="F404" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>550</v>
+      </c>
+      <c r="G404" s="13" t="s">
+        <v>669</v>
+      </c>
+      <c r="H404" s="13"/>
+      <c r="I404" s="13" t="str">
+        <f t="shared" si="30"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J404" s="13">
+        <f t="shared" si="31"/>
+        <v>2026</v>
+      </c>
+      <c r="K404" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L404" s="13"/>
+    </row>
+    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A405" s="12">
+        <v>46185</v>
+      </c>
+      <c r="B405" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C405" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D405" s="14">
+        <v>1</v>
+      </c>
+      <c r="E405" s="15">
+        <v>2</v>
+      </c>
+      <c r="F405" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>2</v>
+      </c>
+      <c r="G405" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H405" s="13"/>
+      <c r="I405" s="13" t="str">
+        <f t="shared" si="30"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J405" s="13">
+        <f t="shared" si="31"/>
+        <v>2026</v>
+      </c>
+      <c r="K405" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L405" s="13"/>
+    </row>
+    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A406" s="12">
+        <v>46174</v>
+      </c>
+      <c r="B406" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C406" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D406" s="14">
+        <v>1</v>
+      </c>
+      <c r="E406" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="F406" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>3.2</v>
+      </c>
+      <c r="G406" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="H406" s="13"/>
+      <c r="I406" s="13" t="str">
+        <f t="shared" si="30"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J406" s="13">
+        <f t="shared" si="31"/>
+        <v>2026</v>
+      </c>
+      <c r="K406" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L406" s="13"/>
+    </row>
+    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A407" s="12">
+        <v>46176</v>
+      </c>
+      <c r="B407" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C407" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D407" s="14">
+        <v>1</v>
+      </c>
+      <c r="E407" s="15">
+        <v>15</v>
+      </c>
+      <c r="F407" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>15</v>
+      </c>
+      <c r="G407" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="H407" s="13"/>
+      <c r="I407" s="13" t="str">
+        <f t="shared" ref="I407:I409" si="32">UPPER(TEXT(A407,"MMMM"))</f>
+        <v>JUNIO</v>
+      </c>
+      <c r="J407" s="13">
+        <f t="shared" ref="J407:J409" si="33">+YEAR(A407)</f>
+        <v>2026</v>
+      </c>
+      <c r="K407" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L407" s="13"/>
+    </row>
+    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A408" s="12">
+        <v>46176</v>
+      </c>
+      <c r="B408" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C408" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D408" s="14">
+        <v>1</v>
+      </c>
+      <c r="E408" s="15">
+        <v>2</v>
+      </c>
+      <c r="F408" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>2</v>
+      </c>
+      <c r="G408" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H408" s="13"/>
+      <c r="I408" s="13" t="str">
+        <f t="shared" si="32"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J408" s="13">
+        <f t="shared" si="33"/>
+        <v>2026</v>
+      </c>
+      <c r="K408" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L408" s="13"/>
+    </row>
+    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A409" s="12">
+        <v>46177</v>
+      </c>
+      <c r="B409" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C409" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D409" s="14">
+        <v>1</v>
+      </c>
+      <c r="E409" s="15">
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="F409" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="G409" s="13" t="s">
+        <v>792</v>
+      </c>
+      <c r="H409" s="13"/>
+      <c r="I409" s="13" t="str">
+        <f t="shared" si="32"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J409" s="13">
+        <f t="shared" si="33"/>
+        <v>2026</v>
+      </c>
+      <c r="K409" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L409" s="13"/>
+    </row>
+    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A410" s="12">
+        <v>46178</v>
+      </c>
+      <c r="B410" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C410" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D410" s="14">
+        <v>1</v>
+      </c>
+      <c r="E410" s="15">
+        <v>10</v>
+      </c>
+      <c r="F410" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>10</v>
+      </c>
+      <c r="G410" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H410" s="13"/>
+      <c r="I410" s="13" t="str">
+        <f t="shared" ref="I410:I412" si="34">UPPER(TEXT(A410,"MMMM"))</f>
+        <v>JUNIO</v>
+      </c>
+      <c r="J410" s="13">
+        <f t="shared" ref="J410:J412" si="35">+YEAR(A410)</f>
+        <v>2026</v>
+      </c>
+      <c r="K410" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L410" s="13"/>
+    </row>
+    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A411" s="12">
+        <v>46181</v>
+      </c>
+      <c r="B411" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C411" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D411" s="14">
+        <v>1</v>
+      </c>
+      <c r="E411" s="15">
+        <v>15</v>
+      </c>
+      <c r="F411" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>15</v>
+      </c>
+      <c r="G411" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H411" s="13"/>
+      <c r="I411" s="13" t="str">
+        <f t="shared" si="34"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J411" s="13">
+        <f t="shared" si="35"/>
+        <v>2026</v>
+      </c>
+      <c r="K411" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L411" s="13"/>
+    </row>
+    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A412" s="12">
+        <v>46181</v>
+      </c>
+      <c r="B412" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C412" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D412" s="14">
+        <v>1</v>
+      </c>
+      <c r="E412" s="15">
+        <v>30</v>
+      </c>
+      <c r="F412" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>30</v>
+      </c>
+      <c r="G412" s="13" t="s">
+        <v>793</v>
+      </c>
+      <c r="H412" s="13"/>
+      <c r="I412" s="13" t="str">
+        <f t="shared" si="34"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J412" s="13">
+        <f t="shared" si="35"/>
+        <v>2026</v>
+      </c>
+      <c r="K412" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L412" s="13"/>
+    </row>
+    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A413" s="12">
+        <v>46181</v>
+      </c>
+      <c r="B413" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C413" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D413" s="14">
+        <v>1</v>
+      </c>
+      <c r="E413" s="15">
+        <v>37</v>
+      </c>
+      <c r="F413" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>37</v>
+      </c>
+      <c r="G413" s="13" t="s">
+        <v>717</v>
+      </c>
+      <c r="H413" s="13"/>
+      <c r="I413" s="13" t="str">
+        <f t="shared" ref="I413:I419" si="36">UPPER(TEXT(A413,"MMMM"))</f>
+        <v>JUNIO</v>
+      </c>
+      <c r="J413" s="13">
+        <f t="shared" ref="J413:J419" si="37">+YEAR(A413)</f>
+        <v>2026</v>
+      </c>
+      <c r="K413" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L413" s="13"/>
+    </row>
+    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A414" s="12">
+        <v>46181</v>
+      </c>
+      <c r="B414" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C414" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D414" s="14">
+        <v>1</v>
+      </c>
+      <c r="E414" s="15">
+        <v>1.4</v>
+      </c>
+      <c r="F414" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>1.4</v>
+      </c>
+      <c r="G414" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="H414" s="13"/>
+      <c r="I414" s="13" t="str">
+        <f t="shared" si="36"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J414" s="13">
+        <f t="shared" si="37"/>
+        <v>2026</v>
+      </c>
+      <c r="K414" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L414" s="13"/>
+    </row>
+    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A415" s="12">
+        <v>46181</v>
+      </c>
+      <c r="B415" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C415" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D415" s="14">
+        <v>1</v>
+      </c>
+      <c r="E415" s="15">
+        <v>17</v>
+      </c>
+      <c r="F415" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>17</v>
+      </c>
+      <c r="G415" s="13" t="s">
+        <v>794</v>
+      </c>
+      <c r="H415" s="13"/>
+      <c r="I415" s="13" t="str">
+        <f t="shared" si="36"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J415" s="13">
+        <f t="shared" si="37"/>
+        <v>2026</v>
+      </c>
+      <c r="K415" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L415" s="13"/>
+    </row>
+    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A416" s="12">
+        <v>46183</v>
+      </c>
+      <c r="B416" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C416" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D416" s="14">
+        <v>1</v>
+      </c>
+      <c r="E416" s="15">
+        <v>90.85</v>
+      </c>
+      <c r="F416" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>90.85</v>
+      </c>
+      <c r="G416" s="13" t="s">
+        <v>576</v>
+      </c>
+      <c r="H416" s="13"/>
+      <c r="I416" s="13" t="str">
+        <f t="shared" si="36"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J416" s="13">
+        <f t="shared" si="37"/>
+        <v>2026</v>
+      </c>
+      <c r="K416" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L416" s="13"/>
+    </row>
+    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A417" s="12">
+        <v>46183</v>
+      </c>
+      <c r="B417" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C417" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D417" s="14">
+        <v>1</v>
+      </c>
+      <c r="E417" s="15">
+        <v>91.32</v>
+      </c>
+      <c r="F417" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>91.32</v>
+      </c>
+      <c r="G417" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="H417" s="13"/>
+      <c r="I417" s="13" t="str">
+        <f t="shared" si="36"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J417" s="13">
+        <f t="shared" si="37"/>
+        <v>2026</v>
+      </c>
+      <c r="K417" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L417" s="13"/>
+    </row>
+    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A418" s="12">
+        <v>46183</v>
+      </c>
+      <c r="B418" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C418" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D418" s="14">
+        <v>1</v>
+      </c>
+      <c r="E418" s="15">
+        <v>29</v>
+      </c>
+      <c r="F418" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>29</v>
+      </c>
+      <c r="G418" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="H418" s="13"/>
+      <c r="I418" s="13" t="str">
+        <f t="shared" si="36"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J418" s="13">
+        <f t="shared" si="37"/>
+        <v>2026</v>
+      </c>
+      <c r="K418" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L418" s="13"/>
+    </row>
+    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A419" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B419" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C419" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D419" s="14">
+        <v>1</v>
+      </c>
+      <c r="E419" s="15">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F419" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="G419" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H419" s="13"/>
+      <c r="I419" s="13" t="str">
+        <f t="shared" si="36"/>
+        <v>MAYO</v>
+      </c>
+      <c r="J419" s="13">
+        <f t="shared" si="37"/>
+        <v>2026</v>
+      </c>
+      <c r="K419" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L419" s="13"/>
+    </row>
+    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A420" s="12">
+        <v>46181</v>
+      </c>
+      <c r="B420" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C420" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D420" s="14">
+        <v>1</v>
+      </c>
+      <c r="E420" s="15">
+        <v>189.25</v>
+      </c>
+      <c r="F420" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>189.25</v>
+      </c>
+      <c r="G420" s="13" t="s">
+        <v>795</v>
+      </c>
+      <c r="H420" s="13"/>
+      <c r="I420" s="13" t="str">
+        <f t="shared" ref="I420:I426" si="38">UPPER(TEXT(A420,"MMMM"))</f>
+        <v>JUNIO</v>
+      </c>
+      <c r="J420" s="13">
+        <f t="shared" ref="J420:J426" si="39">+YEAR(A420)</f>
+        <v>2026</v>
+      </c>
+      <c r="K420" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L420" s="13"/>
+    </row>
+    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A421" s="12">
+        <v>46181</v>
+      </c>
+      <c r="B421" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C421" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D421" s="14">
+        <v>1</v>
+      </c>
+      <c r="E421" s="15">
+        <v>100.41</v>
+      </c>
+      <c r="F421" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>100.41</v>
+      </c>
+      <c r="G421" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="H421" s="13"/>
+      <c r="I421" s="13" t="str">
+        <f t="shared" si="38"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J421" s="13">
+        <f t="shared" si="39"/>
+        <v>2026</v>
+      </c>
+      <c r="K421" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L421" s="13"/>
+    </row>
+    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A422" s="12">
+        <v>46182</v>
+      </c>
+      <c r="B422" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C422" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D422" s="14">
+        <v>1</v>
+      </c>
+      <c r="E422" s="15">
+        <v>1000.41</v>
+      </c>
+      <c r="F422" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>1000.41</v>
+      </c>
+      <c r="G422" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="H422" s="13"/>
+      <c r="I422" s="13" t="str">
+        <f t="shared" si="38"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J422" s="13">
+        <f t="shared" si="39"/>
+        <v>2026</v>
+      </c>
+      <c r="K422" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L422" s="13"/>
+    </row>
+    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A423" s="12">
+        <v>46178</v>
+      </c>
+      <c r="B423" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C423" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D423" s="14">
+        <v>1</v>
+      </c>
+      <c r="E423" s="15">
+        <v>500.41</v>
+      </c>
+      <c r="F423" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>500.41</v>
+      </c>
+      <c r="G423" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="H423" s="13"/>
+      <c r="I423" s="13" t="str">
+        <f t="shared" si="38"/>
+        <v>JUNIO</v>
+      </c>
+      <c r="J423" s="13">
+        <f t="shared" si="39"/>
+        <v>2026</v>
+      </c>
+      <c r="K423" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="L423" s="13"/>
+    </row>
+    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A424" s="12">
+        <v>46165</v>
+      </c>
+      <c r="B424" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C424" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D424" s="14">
+        <v>1</v>
+      </c>
+      <c r="E424" s="15">
+        <v>60.41</v>
+      </c>
+      <c r="F424" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>60.41</v>
+      </c>
+      <c r="G424" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="H424" s="13"/>
+      <c r="I424" s="13" t="str">
+        <f t="shared" si="38"/>
+        <v>MAYO</v>
+      </c>
+      <c r="J424" s="13">
+        <f t="shared" si="39"/>
+        <v>2026</v>
+      </c>
+      <c r="K424" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="L424" s="13"/>
+    </row>
+    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A425" s="12">
+        <v>46165</v>
+      </c>
+      <c r="B425" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C425" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D425" s="14">
+        <v>1</v>
+      </c>
+      <c r="E425" s="15">
+        <v>30.41</v>
+      </c>
+      <c r="F425" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>30.41</v>
+      </c>
+      <c r="G425" s="13" t="s">
+        <v>797</v>
+      </c>
+      <c r="H425" s="13"/>
+      <c r="I425" s="13" t="str">
+        <f t="shared" si="38"/>
+        <v>MAYO</v>
+      </c>
+      <c r="J425" s="13">
+        <f t="shared" si="39"/>
+        <v>2026</v>
+      </c>
+      <c r="K425" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="L425" s="13"/>
+    </row>
+    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A426" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B426" s="68"/>
+      <c r="C426" s="13"/>
+      <c r="D426" s="14"/>
+      <c r="E426" s="15"/>
+      <c r="F426" s="15">
+        <f>Tabla8[[#This Row],[CANTIDAD]]*Tabla8[[#This Row],[PRECIO]]</f>
+        <v>0</v>
+      </c>
+      <c r="G426" s="13"/>
+      <c r="H426" s="13"/>
+      <c r="I426" s="13" t="str">
+        <f t="shared" si="38"/>
+        <v>MAYO</v>
+      </c>
+      <c r="J426" s="13">
+        <f t="shared" si="39"/>
+        <v>2026</v>
+      </c>
+      <c r="K426" s="13"/>
+      <c r="L426" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -32652,13 +35134,13 @@
           <x14:formula1>
             <xm:f>'CUENTAS CONTABLES'!$C$5:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>B4:B387</xm:sqref>
+          <xm:sqref>B4:B426</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1B36022B-D017-4A30-A926-A6D8157B0AF1}">
           <x14:formula1>
             <xm:f>'CUENTAS CONTABLES'!$G$5:$G$11</xm:f>
           </x14:formula1>
-          <xm:sqref>K4:K387</xm:sqref>
+          <xm:sqref>K4:K426</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A72FD84C-357E-493F-B119-CCBA33DC70B9}">
           <x14:formula1>
@@ -40014,7 +42496,7 @@
       </c>
       <c r="F155" s="59">
         <f ca="1">NOW()</f>
-        <v>46183.505807638889</v>
+        <v>46195.555982175923</v>
       </c>
     </row>
     <row r="157" spans="1:14" ht="26.25" x14ac:dyDescent="0.4">
@@ -40924,7 +43406,7 @@
       </c>
       <c r="F195" s="59">
         <f ca="1">NOW()</f>
-        <v>46183.505807638889</v>
+        <v>46195.555982175923</v>
       </c>
     </row>
   </sheetData>
